--- a/data/macro/USA/US Consumer Confidence.xlsx
+++ b/data/macro/USA/US Consumer Confidence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4925E497-7EF1-44F0-8CF3-FF7CD9174F37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B6688C-2D04-48C6-9F11-AF0194AF6B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22605" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
   </bookViews>
@@ -15516,8 +15516,14 @@
         <f t="shared" si="10"/>
         <v>UTC-5</v>
       </c>
+      <c r="E675" s="8">
+        <v>91.2</v>
+      </c>
+      <c r="F675" s="8">
+        <v>87.4</v>
+      </c>
       <c r="G675" s="8">
-        <v>84.5</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/US Consumer Confidence.xlsx
+++ b/data/macro/USA/US Consumer Confidence.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B6688C-2D04-48C6-9F11-AF0194AF6B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B008FD6-A2A2-41E3-9FD4-A93BC8427411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22605" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
   </bookViews>
   <sheets>
     <sheet name="CONCCONF" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -511,14 +520,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0F7D99-AC79-884E-BA11-A70B8FD1EA94}">
-  <dimension ref="A1:G675"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G677"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="7"/>
-    <col min="5" max="7" width="10.88671875" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="5"/>
+    <col min="1" max="2" width="12.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="7"/>
+    <col min="5" max="7" width="10.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.54296875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -14730,7 +14739,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D643" s="7" t="str">
-        <f t="shared" ref="D643:D675" si="10">IF(
+        <f t="shared" ref="D643:D677" si="10">IF(
  AND(
   B643 &gt;= IF(
          YEAR(B643)&gt;=2007,
@@ -15526,6 +15535,48 @@
         <v>89</v>
       </c>
     </row>
+    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A676" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B676" s="6">
+        <v>46112</v>
+      </c>
+      <c r="C676" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D676" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E676" s="8">
+        <v>91.8</v>
+      </c>
+      <c r="F676" s="8">
+        <v>87.8</v>
+      </c>
+      <c r="G676" s="8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A677" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B677" s="6">
+        <v>46140</v>
+      </c>
+      <c r="C677" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D677" s="7" t="str">
+        <f t="shared" si="10"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G677" s="8">
+        <v>91.8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15536,9 +15587,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A371B19D-AA7E-B447-A255-24E7D00A18A4}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
@@ -15546,7 +15597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>

--- a/data/macro/USA/US Consumer Confidence.xlsx
+++ b/data/macro/USA/US Consumer Confidence.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B008FD6-A2A2-41E3-9FD4-A93BC8427411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDD8C3-4FB7-4D75-A1B3-8BD27767E043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBE3001D-16D9-CC45-A2DD-41E4392F3541}"/>
   </bookViews>
@@ -15573,8 +15573,14 @@
         <f t="shared" si="10"/>
         <v>UTC-4</v>
       </c>
+      <c r="E677" s="8">
+        <v>92.8</v>
+      </c>
+      <c r="F677" s="8">
+        <v>89</v>
+      </c>
       <c r="G677" s="8">
-        <v>91.8</v>
+        <v>92.2</v>
       </c>
     </row>
   </sheetData>
